--- a/api/templates/mtb_detected_rr_detected/mw/en.xlsx
+++ b/api/templates/mtb_detected_rr_detected/mw/en.xlsx
@@ -136,13 +136,13 @@
     <t>Received by</t>
   </si>
   <si>
-    <t>&lt;sampleCollectedOn&gt;</t>
-  </si>
-  <si>
-    <t>&lt;resultWorkflowLogCreatedOn&gt;</t>
-  </si>
-  <si>
-    <t>&lt;resultWorkflowLogOperator&gt;</t>
+    <t>&lt;dateOfSampleCollection&gt;</t>
+  </si>
+  <si>
+    <t>&lt;dateOfReceiptInTheLab&gt;</t>
+  </si>
+  <si>
+    <t>&lt;receivedBy&gt;</t>
   </si>
 </sst>
 </file>

--- a/api/templates/mtb_detected_rr_detected/mw/en.xlsx
+++ b/api/templates/mtb_detected_rr_detected/mw/en.xlsx
@@ -1,44 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-2\api\templates\mtb_detected_rr_detected\mw\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12936" tabRatio="500"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
-  <si>
-    <t>MTB Detected, RR Detected</t>
-  </si>
-  <si>
-    <t>Date Range: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+  <si>
+    <t xml:space="preserve">MTB Detected, RR Detected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date Range: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
     <t>&lt;UserFullName&gt;</t>
@@ -50,16 +39,16 @@
     <t>#</t>
   </si>
   <si>
-    <t>Patient ID</t>
-  </si>
-  <si>
-    <t>Patient ID 2</t>
-  </si>
-  <si>
-    <t>Case ID</t>
-  </si>
-  <si>
-    <t>Sample ID</t>
+    <t xml:space="preserve">Patient ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient ID 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample ID</t>
   </si>
   <si>
     <t>Age</t>
@@ -68,7 +57,24 @@
     <t>Device</t>
   </si>
   <si>
-    <t>Test Date</t>
+    <t xml:space="preserve">Machine Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assay Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date of 
+sample collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date of Receipt
+ in the Lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received by</t>
   </si>
   <si>
     <t>MTB</t>
@@ -77,13 +83,13 @@
     <t>RIF</t>
   </si>
   <si>
-    <t>Result Text</t>
-  </si>
-  <si>
-    <t>Error Code</t>
-  </si>
-  <si>
-    <t>Test Notes</t>
+    <t xml:space="preserve">Result Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Notes</t>
   </si>
   <si>
     <t>&lt;#&gt;</t>
@@ -107,9 +113,24 @@
     <t>&lt;deviceName&gt;</t>
   </si>
   <si>
+    <t>&lt;instrumentSerial&gt;</t>
+  </si>
+  <si>
     <t>&lt;endedOn&gt;</t>
   </si>
   <si>
+    <t>&lt;assayName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;dateOfSampleCollection&gt;</t>
+  </si>
+  <si>
+    <t>&lt;dateOfReceiptInTheLab&gt;</t>
+  </si>
+  <si>
+    <t>&lt;receivedBy&gt;</t>
+  </si>
+  <si>
     <t>&lt;resultCategory1Name&gt;</t>
   </si>
   <si>
@@ -123,79 +144,40 @@
   </si>
   <si>
     <t>&lt;notes&gt;</t>
-  </si>
-  <si>
-    <t>Date of 
-sample collection</t>
-  </si>
-  <si>
-    <t>Date of Receipt
- in the Lab</t>
-  </si>
-  <si>
-    <t>Received by</t>
-  </si>
-  <si>
-    <t>&lt;dateOfSampleCollection&gt;</t>
-  </si>
-  <si>
-    <t>&lt;dateOfReceiptInTheLab&gt;</t>
-  </si>
-  <si>
-    <t>&lt;receivedBy&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="11.000000"/>
+      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="12.000000"/>
+      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
+      <sz val="16.000000"/>
+      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
+      <sz val="12.000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="12.000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -208,17 +190,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF3CC0DD"/>
-        <bgColor rgb="FF00CCFF"/>
+        <bgColor indexed="40"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="3">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -233,7 +215,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
@@ -248,42 +230,44 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="16">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="4" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf fontId="4" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -296,7 +280,8 @@
         <i val="0"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD7D7D7"/>
           <bgColor rgb="FFD7D7D7"/>
         </patternFill>
       </fill>
@@ -307,99 +292,312 @@
         <i val="0"/>
       </font>
       <fill>
-        <patternFill patternType="none">
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
+    <tableStyle name="MySqlDefault" table="0" pivot="0" count="2">
+      <tableStyleElement type="headerRow" size="1" dxfId="0"/>
+      <tableStyleElement type="wholeTable" size="1" dxfId="1"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -441,108 +639,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -550,7 +654,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -576,7 +680,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -628,16 +732,28 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -653,7 +769,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -684,32 +800,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" customWidth="1"/>
-    <col min="2" max="4" width="24.21875" customWidth="1"/>
-    <col min="5" max="5" width="23.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="11" width="18.44140625" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="15" width="16.77734375" customWidth="1"/>
-    <col min="16" max="16" width="60.77734375" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="7.44140625"/>
+    <col customWidth="1" min="2" max="4" width="24.21875"/>
+    <col customWidth="1" min="5" max="5" width="23.109375"/>
+    <col customWidth="1" min="6" max="6" style="1" width="15.88671875"/>
+    <col customWidth="1" min="7" max="8" width="28"/>
+    <col customWidth="1" min="9" max="13" width="18.44140625"/>
+    <col customWidth="1" min="14" max="14" width="14.44140625"/>
+    <col customWidth="1" min="15" max="17" width="16.77734375"/>
+    <col customWidth="1" min="18" max="18" width="60.77734375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -728,8 +837,10 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
     </row>
-    <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" ht="16.5">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -748,8 +859,10 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
     </row>
-    <row r="3" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" ht="16.5">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -768,8 +881,10 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
     </row>
-    <row r="4" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" ht="16.5">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -788,8 +903,10 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
     </row>
-    <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" ht="16.5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -808,8 +925,10 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
     </row>
-    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" ht="16.5">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -826,8 +945,10 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
     </row>
-    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" ht="16.5">
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
@@ -845,8 +966,10 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
     </row>
-    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" ht="16.5">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -866,9 +989,11 @@
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
-      <c r="P8" s="6"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:16" ht="30.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" ht="30.899999999999999" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
@@ -893,83 +1018,97 @@
       <c r="H9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5">
+      <c r="A10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J10" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="12" t="s">
+      <c r="L10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="M10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="N10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="L10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>32</v>
+      <c r="O10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R10" s="12" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/api/templates/mtb_detected_rr_detected/mw/en.xlsx
+++ b/api/templates/mtb_detected_rr_detected/mw/en.xlsx
@@ -1,33 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="Results" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
-  <si>
-    <t xml:space="preserve">MTB Detected, RR Detected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date Range: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;StatesLabel&gt;: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+  <si>
+    <t>MTB Detected, RR Detected</t>
+  </si>
+  <si>
+    <t>Date Range: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
     <t>&lt;UserFullName&gt;</t>
@@ -39,16 +40,16 @@
     <t>#</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient ID 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Case ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample ID</t>
+    <t>Patient ID</t>
+  </si>
+  <si>
+    <t>Patient ID 2</t>
+  </si>
+  <si>
+    <t>Case ID</t>
+  </si>
+  <si>
+    <t>Sample ID</t>
   </si>
   <si>
     <t>Age</t>
@@ -57,13 +58,16 @@
     <t>Device</t>
   </si>
   <si>
-    <t xml:space="preserve">Machine Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assay Name</t>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Machine Id</t>
+  </si>
+  <si>
+    <t>Test Date</t>
+  </si>
+  <si>
+    <t>Assay Name</t>
   </si>
   <si>
     <t xml:space="preserve">Date of 
@@ -74,7 +78,7 @@
  in the Lab</t>
   </si>
   <si>
-    <t xml:space="preserve">Received by</t>
+    <t>Received by</t>
   </si>
   <si>
     <t>MTB</t>
@@ -83,13 +87,13 @@
     <t>RIF</t>
   </si>
   <si>
-    <t xml:space="preserve">Result Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Notes</t>
+    <t>Result Text</t>
+  </si>
+  <si>
+    <t>Error Code</t>
+  </si>
+  <si>
+    <t>Test Notes</t>
   </si>
   <si>
     <t>&lt;#&gt;</t>
@@ -111,6 +115,9 @@
   </si>
   <si>
     <t>&lt;deviceName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;instrumentSerial&gt;</t>
@@ -149,34 +156,41 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd-mm-yyyy;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
-      <color indexed="64"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12.000000"/>
       <color indexed="64"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.000000"/>
       <color indexed="64"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color indexed="64"/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -194,7 +208,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -203,111 +224,66 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="4" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf fontId="4" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD7D7D7"/>
-          <bgColor rgb="FFD7D7D7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="65"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" table="0" pivot="0" count="2">
-      <tableStyleElement type="headerRow" size="1" dxfId="0"/>
-      <tableStyleElement type="wholeTable" size="1" dxfId="1"/>
-    </tableStyle>
-  </tableStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -804,21 +780,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S12"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.77734375" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.44140625"/>
-    <col customWidth="1" min="2" max="4" width="24.21875"/>
-    <col customWidth="1" min="5" max="5" width="23.109375"/>
-    <col customWidth="1" min="6" max="6" style="1" width="15.88671875"/>
-    <col customWidth="1" min="7" max="8" width="28"/>
-    <col customWidth="1" min="9" max="13" width="18.44140625"/>
-    <col customWidth="1" min="14" max="14" width="14.44140625"/>
-    <col customWidth="1" min="15" max="17" width="16.77734375"/>
-    <col customWidth="1" min="18" max="18" width="60.77734375"/>
+    <col min="1" max="1" width="7.44140625" customWidth="1"/>
+    <col min="2" max="4" width="24.21875" customWidth="1"/>
+    <col min="5" max="5" width="23.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="14" width="18.44140625" customWidth="1"/>
+    <col min="15" max="15" width="14.44140625" customWidth="1"/>
+    <col min="16" max="18" width="16.77734375" customWidth="1"/>
+    <col min="19" max="19" width="60.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1" ht="21" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -840,7 +819,7 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
     </row>
-    <row r="2" ht="16.5">
+    <row r="2" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -862,7 +841,7 @@
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
     </row>
-    <row r="3" ht="16.5">
+    <row r="3" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -884,7 +863,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
     </row>
-    <row r="4" ht="16.5">
+    <row r="4" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -906,7 +885,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
     </row>
-    <row r="5" ht="16.5">
+    <row r="5" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -928,7 +907,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
     </row>
-    <row r="6" ht="16.5">
+    <row r="6" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -948,7 +927,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
     </row>
-    <row r="7" ht="16.5">
+    <row r="7" ht="16.5" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
@@ -969,7 +948,7 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
     </row>
-    <row r="8" ht="16.5">
+    <row r="8" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -993,7 +972,7 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" ht="30.899999999999999" customHeight="1">
+    <row r="9" ht="30.9" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
@@ -1024,16 +1003,16 @@
       <c r="J9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="N9" s="8" t="s">
         <v>20</v>
       </c>
       <c r="O9" s="9" t="s">
@@ -1048,67 +1027,73 @@
       <c r="R9" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="S9" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="10" ht="16.5">
+    <row r="10" ht="16.5" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="H10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="I10" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="J10" s="14" t="s">
         <v>35</v>
       </c>
+      <c r="K10" s="15" t="s">
+        <v>36</v>
+      </c>
       <c r="L10" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="N10" s="12" t="s">
         <v>38</v>
       </c>
+      <c r="N10" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="O10" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R10" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="S10" s="12" t="s">
+        <v>44</v>
       </c>
     </row>
+    <row r="11" spans="8:19" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="8:19" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/mtb_detected_rr_detected/mw/en.xlsx
+++ b/api/templates/mtb_detected_rr_detected/mw/en.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B90D14-CD67-2D42-A3AB-BB9FF0E016D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Results" state="visible" r:id="rId4"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -70,11 +71,11 @@
     <t>Assay Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of 
+    <t>Date of 
 sample collection</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of Receipt
+    <t>Date of Receipt
  in the Lab</t>
   </si>
   <si>
@@ -156,42 +157,47 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd-mm-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color indexed="64"/>
-      <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
       <color indexed="64"/>
-      <sz val="16"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="12"/>
       <color indexed="64"/>
-      <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -217,25 +223,41 @@
       <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -289,291 +311,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -776,28 +515,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S12"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.77734375" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" customWidth="1"/>
-    <col min="2" max="4" width="24.21875" customWidth="1"/>
-    <col min="5" max="5" width="23.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="1" max="1" width="7.5" customWidth="1"/>
+    <col min="2" max="4" width="24.1640625" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="14" width="18.44140625" customWidth="1"/>
-    <col min="15" max="15" width="14.44140625" customWidth="1"/>
-    <col min="16" max="18" width="16.77734375" customWidth="1"/>
-    <col min="19" max="19" width="60.77734375" customWidth="1"/>
+    <col min="10" max="14" width="18.5" customWidth="1"/>
+    <col min="15" max="15" width="14.5" customWidth="1"/>
+    <col min="16" max="18" width="16.83203125" customWidth="1"/>
+    <col min="19" max="19" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -819,7 +559,7 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -841,7 +581,7 @@
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
     </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -863,7 +603,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
     </row>
-    <row r="4" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -885,7 +625,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
     </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -907,7 +647,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
     </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -927,7 +667,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
     </row>
-    <row r="7" ht="16.5" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
@@ -948,7 +688,7 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
     </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -972,7 +712,7 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" ht="30.9" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
@@ -1031,7 +771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
@@ -1090,10 +830,10 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="8:19" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="8:19" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:19" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:19" ht="15" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>